--- a/templates/FIMEMBVIIACP - template.xlsx
+++ b/templates/FIMEMBVIIACP - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="55" min="1" max="1"/>
@@ -1238,8 +1238,8 @@
     <col width="5.42578125" customWidth="1" style="55" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="55" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="55" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="55" min="10" max="16"/>
-    <col width="9.140625" customWidth="1" style="55" min="17" max="16384"/>
+    <col width="9.140625" customWidth="1" style="55" min="10" max="17"/>
+    <col width="9.140625" customWidth="1" style="55" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1382,96 +1382,96 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="35" t="n">
-        <v>151.5123968</v>
+        <v>154.3085066</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>-0.002833273690091564</v>
+        <v>0.001134262814599607</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.0004925342348984785</v>
+        <v>0.0004308998088589089</v>
       </c>
       <c r="F17" s="37" t="n">
-        <v>-5.752440113478733</v>
+        <v>2.632312178562611</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B18" s="38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="39" t="n">
-        <v>151.9428926</v>
+        <v>154.1336785</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0.001792092420200397</v>
+        <v>0.0007524695940179793</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0.0004925342348984785</v>
+        <v>0.0004308998088589089</v>
       </c>
       <c r="F18" s="41" t="n">
-        <v>3.63851341332605</v>
+        <v>1.746275070324673</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B19" s="38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="39" t="n">
-        <v>151.671084</v>
+        <v>154.0177848</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>-0.001202906744945609</v>
+        <v>0.005064220269408892</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0.0004925342348984785</v>
+        <v>0.0004308998088589089</v>
       </c>
       <c r="F19" s="41" t="n">
-        <v>-2.442280474561434</v>
+        <v>11.75266306759279</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="39" t="n">
-        <v>151.8537499</v>
+        <v>153.2417349</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0.002572131845937964</v>
+        <v>-0.0009028211669585007</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0.0004925342348984785</v>
+        <v>0.0004308998088589089</v>
       </c>
       <c r="F20" s="41" t="n">
-        <v>5.222239722012691</v>
+        <v>-2.095199738772952</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B21" s="38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="39" t="n">
-        <v>151.4641641</v>
+        <v>153.3802098</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>-0.002902627593356244</v>
+        <v>0.002619192305385987</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>0.0004925342348984785</v>
+        <v>0.0004308998088589089</v>
       </c>
       <c r="F21" s="41" t="n">
-        <v>-5.893250433555214</v>
+        <v>6.078425312654521</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1511,18 +1511,18 @@
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B24" s="42" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="42" t="inlineStr"/>
       <c r="D24" s="36" t="n">
-        <v>-0.00325604278454461</v>
+        <v>0.008451216676962137</v>
       </c>
       <c r="E24" s="36" t="n">
-        <v>0.009399749356682863</v>
+        <v>0.003020200631021153</v>
       </c>
       <c r="F24" s="37" t="n">
-        <v>-0.3463967666573671</v>
+        <v>2.79823022025683</v>
       </c>
       <c r="G24" s="43" t="n"/>
     </row>
@@ -1535,13 +1535,13 @@
       </c>
       <c r="C25" s="45" t="inlineStr"/>
       <c r="D25" s="40" t="n">
-        <v>-0.001210197536752222</v>
+        <v>0.0176104014830869</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>0.01053772583172718</v>
+        <v>0.0121671107114012</v>
       </c>
       <c r="F25" s="41" t="n">
-        <v>-0.1148442800730815</v>
+        <v>1.447377434199318</v>
       </c>
       <c r="G25" s="46" t="n"/>
       <c r="H25" s="47" t="n"/>
@@ -1555,13 +1555,13 @@
       </c>
       <c r="C26" s="45" t="inlineStr"/>
       <c r="D26" s="40" t="n">
-        <v>0.03112575946968343</v>
+        <v>0.0443623130763886</v>
       </c>
       <c r="E26" s="40" t="n">
-        <v>0.03002932592080332</v>
+        <v>0.03420344006821918</v>
       </c>
       <c r="F26" s="41" t="n">
-        <v>1.036512093270817</v>
+        <v>1.297013194810447</v>
       </c>
       <c r="G26" s="46" t="n"/>
     </row>
@@ -1574,13 +1574,13 @@
       </c>
       <c r="C27" s="45" t="inlineStr"/>
       <c r="D27" s="40" t="n">
-        <v>0.05927975148760312</v>
+        <v>0.07555980798561657</v>
       </c>
       <c r="E27" s="40" t="n">
-        <v>0.05163445571420922</v>
+        <v>0.05631847919317901</v>
       </c>
       <c r="F27" s="41" t="n">
-        <v>1.148065776382146</v>
+        <v>1.341652137417233</v>
       </c>
       <c r="G27" s="46" t="n"/>
     </row>
@@ -1593,13 +1593,13 @@
       </c>
       <c r="C28" s="45" t="inlineStr"/>
       <c r="D28" s="40" t="n">
-        <v>0.1529309744638816</v>
+        <v>0.1669797274548772</v>
       </c>
       <c r="E28" s="40" t="n">
-        <v>0.09975868494595241</v>
+        <v>0.1034873929584561</v>
       </c>
       <c r="F28" s="41" t="n">
-        <v>1.533009126440841</v>
+        <v>1.613527239225259</v>
       </c>
       <c r="G28" s="46" t="n"/>
     </row>
@@ -1607,18 +1607,18 @@
       <c r="A29" s="48" t="n"/>
       <c r="B29" s="45" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="45" t="inlineStr"/>
       <c r="D29" s="40" t="n">
-        <v>0.02624914677413415</v>
+        <v>0.2353548488192312</v>
       </c>
       <c r="E29" s="40" t="n">
-        <v>0.02803245743716443</v>
+        <v>0.2331517508618997</v>
       </c>
       <c r="F29" s="41" t="n">
-        <v>0.9363840766715646</v>
+        <v>1.009449201857534</v>
       </c>
       <c r="G29" s="46" t="n"/>
     </row>
@@ -1626,18 +1626,18 @@
       <c r="A30" s="48" t="n"/>
       <c r="B30" s="45" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="45" t="inlineStr"/>
       <c r="D30" s="40" t="n">
-        <v>0.1609597771692761</v>
+        <v>0.0451882260649501</v>
       </c>
       <c r="E30" s="40" t="n">
-        <v>0.1042657310150845</v>
+        <v>0.03621228344143779</v>
       </c>
       <c r="F30" s="41" t="n">
-        <v>1.543745731241164</v>
+        <v>1.247870108440638</v>
       </c>
       <c r="G30" s="46" t="n"/>
     </row>
@@ -1645,18 +1645,18 @@
       <c r="A31" s="48" t="n"/>
       <c r="B31" s="45" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="45" t="inlineStr"/>
       <c r="D31" s="40" t="n">
-        <v>0.05363071528485608</v>
+        <v>0.1609597771692761</v>
       </c>
       <c r="E31" s="40" t="n">
-        <v>0.1113897041597771</v>
+        <v>0.1042657310150845</v>
       </c>
       <c r="F31" s="41" t="n">
-        <v>0.4814692317337365</v>
+        <v>1.543745731241164</v>
       </c>
       <c r="G31" s="46" t="n"/>
     </row>
@@ -1664,166 +1664,185 @@
       <c r="A32" s="48" t="n"/>
       <c r="B32" s="45" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="45" t="inlineStr"/>
       <c r="D32" s="40" t="n">
-        <v>0.5151239680000002</v>
+        <v>0.05363071528485608</v>
       </c>
       <c r="E32" s="40" t="n">
-        <v>0.7270573623409853</v>
+        <v>0.1113897041597771</v>
       </c>
       <c r="F32" s="41" t="n">
-        <v>0.7085052633830703</v>
+        <v>0.4814692317337365</v>
       </c>
       <c r="G32" s="46" t="n"/>
     </row>
-    <row r="33" ht="15.95" customHeight="1">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
+    <row r="33" ht="15.95" customFormat="1" customHeight="1" s="33">
+      <c r="A33" s="48" t="n"/>
+      <c r="B33" s="45" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="45" t="inlineStr"/>
+      <c r="D33" s="40" t="n">
+        <v>0.5430850659999999</v>
+      </c>
+      <c r="E33" s="40" t="n">
+        <v>0.7407991743053339</v>
+      </c>
+      <c r="F33" s="41" t="n">
+        <v>0.733107007724819</v>
+      </c>
+      <c r="G33" s="46" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customHeight="1">
       <c r="A34" s="12" t="n"/>
-      <c r="B34" s="54" t="inlineStr">
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="A35" s="12" t="n"/>
+      <c r="B35" s="54" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="49" t="n">
-        <v>58707726.58</v>
-      </c>
-      <c r="F35" s="30" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="16" t="n"/>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C36" s="15" t="n"/>
       <c r="D36" s="15" t="n"/>
       <c r="E36" s="49" t="n">
-        <v>88718374.36361112</v>
+        <v>59791157.73</v>
       </c>
       <c r="F36" s="30" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="16" t="n"/>
-      <c r="B37" s="18" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="49" t="n">
+        <v>86967550.02496031</v>
+      </c>
+      <c r="F37" s="30" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="A38" s="16" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="A39" s="22" t="n"/>
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="21" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>2021-05-28</t>
         </is>
       </c>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="23" t="n"/>
-      <c r="F39" s="23" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="24" t="n"/>
-      <c r="C40" s="25" t="n"/>
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="23" t="n"/>
       <c r="F40" s="23" t="n"/>
       <c r="G40" s="4" t="n"/>
     </row>
-    <row r="41" ht="54" customHeight="1">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="56" t="inlineStr">
+    <row r="41" ht="15.95" customHeight="1">
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="25" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="54" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="56" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="57" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="26" t="n"/>
-      <c r="C43" s="26" t="n"/>
-      <c r="D43" s="26" t="n"/>
-      <c r="E43" s="26" t="n"/>
-      <c r="F43" s="26" t="n"/>
+      <c r="B43" s="57" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="27" t="n"/>
-      <c r="C44" s="28" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
+      <c r="B44" s="26" t="n"/>
+      <c r="C44" s="26" t="n"/>
+      <c r="D44" s="26" t="n"/>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="26" t="n"/>
       <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="27" t="n"/>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="86" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="83"/>
 </worksheet>
 </file>